--- a/calibrated-claims.xlsx
+++ b/calibrated-claims.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D656454-D7F1-EE44-A3D5-CE1428CA19DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673582E2-B1BE-224E-90D6-61D56D880E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34400" yWindow="600" windowWidth="34400" windowHeight="28200" xr2:uid="{3E7D937B-A97C-9B4F-ABFE-17D590DDFA0D}"/>
+    <workbookView xWindow="16400" yWindow="3400" windowWidth="36000" windowHeight="22600" xr2:uid="{3E7D937B-A97C-9B4F-ABFE-17D590DDFA0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
-  <si>
-    <t>Original</t>
-  </si>
-  <si>
-    <t>Reproduction</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Reproduction target</t>
   </si>
@@ -86,9 +80,6 @@
     <t>Krichene &amp; Rendle (2020)</t>
   </si>
   <si>
-    <t>"Findings from sampled etrics (even in expectation) can be inconsistent with exact metrics." p. 1748, Introduction; formalized in Sec. 4.1.</t>
-  </si>
-  <si>
     <t>Dallmann et al. (2021)</t>
   </si>
   <si>
@@ -176,12 +167,37 @@
     <t>Other implementations and later models; conditions for convergence across all datasets; original ablation claims; generalization beyond the reviewed comparisons.</t>
   </si>
   <si>
-    <t>Original claim 
-(refers to column A)</t>
-  </si>
-  <si>
-    <t>Reproduction Result 
-(refers to column C)</t>
+    <t>Original claim</t>
+  </si>
+  <si>
+    <t>Original paper</t>
+  </si>
+  <si>
+    <t>Follow-up paper</t>
+  </si>
+  <si>
+    <t>Reported results</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>MovieLens-1M and Pinterest; NCF models compared with eALS and BPR; sampled-candidate evaluation; HR@10 and NDCG@10; original training and tuning setup.</t>
+  </si>
+  <si>
+    <t>Item recommendation with sampled candidate sets; sampled ranking metrics compared with exact full-item evaluation under the conditions analyzed in the original study.</t>
+  </si>
+  <si>
+    <t>ReDial conversational recommendation; KBRD compared with the original baselines; automatic recommendation and generation measures and human consistency ratings; original data and training setup.</t>
+  </si>
+  <si>
+    <t>MovieLens-1M and Pinterest; dot-product MF compared with MLP-based models and NeuMF; sampled-candidate evaluation; HR@10 and NDCG@10; tuned model configurations.</t>
+  </si>
+  <si>
+    <t>Four sequential-recommendation datasets; BERT4Rec compared with established sequential and non-sequential baselines, including SASRec; original preprocessing, training, and evaluation protocol.</t>
+  </si>
+  <si>
+    <t>"Findings from sampled metrics (even in expectation) can be inconsistent with exact metrics." p. 1748, Introduction; formalized in Sec. 4.1.</t>
   </si>
 </sst>
 </file>
@@ -245,21 +261,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -271,11 +284,63 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thick">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thick">
+          <color indexed="64"/>
+        </left>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -290,47 +355,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thick">
-          <color indexed="64"/>
-        </left>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thick">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -346,8 +370,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A4ED91C5-E96F-644B-8E54-1424A31AF848}" name="Table3" displayName="Table3" ref="A1:H6" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:H6" xr:uid="{A4ED91C5-E96F-644B-8E54-1424A31AF848}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A4ED91C5-E96F-644B-8E54-1424A31AF848}" name="Table3" displayName="Table3" ref="A1:I6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I6" xr:uid="{A4ED91C5-E96F-644B-8E54-1424A31AF848}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -356,14 +380,16 @@
     <filterColumn colId="5" hiddenButton="1"/>
     <filterColumn colId="6" hiddenButton="1"/>
     <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A1E0514E-950C-D643-9E47-FE2B7CA5EEFE}" name="Original" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{700DFCAC-7F87-2840-B8A0-792A0A3026E9}" name="Original claim _x000a_(refers to column A)" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{A373AF1A-8DC3-694B-BF2C-7F6E49558A63}" name="Reproduction" dataDxfId="7"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A1E0514E-950C-D643-9E47-FE2B7CA5EEFE}" name="Original paper" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{3242A62D-3D10-0143-9665-D7089AC73379}" name="Original claim" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{700DFCAC-7F87-2840-B8A0-792A0A3026E9}" name="Scope" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{A373AF1A-8DC3-694B-BF2C-7F6E49558A63}" name="Follow-up paper" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{9965C936-3A92-E54E-9444-48D4DFA173CB}" name="Reproduction target" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{74265791-CAE5-0246-B614-61BFB8DDA5F4}" name="Study relationship" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{3326A75B-0EED-9E45-9CF2-2E6F9B20CA70}" name="Reproduction Result _x000a_(refers to column C)" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{3326A75B-0EED-9E45-9CF2-2E6F9B20CA70}" name="Reported results" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{2D44BDB6-6D0D-6944-88B2-F3B0E07A0AA5}" name="Calibrated claim" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{C84AE244-C608-B14C-A812-1F6D86E7CFC9}" name="Unresolved scope" dataDxfId="2"/>
   </tableColumns>
@@ -688,173 +714,192 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05ED71E-E8A0-874B-8C57-CD91C66D7DED}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="30.33203125" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.5" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="7" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="124" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:9" ht="149" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="152" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="132" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>13</v>
+      <c r="B5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="161" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="145" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="4" t="s">
+    <row r="6" spans="1:9" ht="161" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="193" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
